--- a/datos/plantilla_salvamed.xlsx
+++ b/datos/plantilla_salvamed.xlsx
@@ -475,7 +475,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Historial diario: ventas de días completos (una fila por día y medicamento). No mueve existencias: solo alimenta μD y σD.</t>
+          <t xml:space="preserve">  Historial diario: unidades despachadas a los servicios en días completos (una fila por día y medicamento). No mueve existencias: solo alimenta μD y σD.</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Un día observado sin ventas se escribe con cantidad 0; un día sin registro simplemente no se escribe.</t>
+          <t>Un día observado sin despachos se escribe con cantidad 0; un día sin registro simplemente no se escribe.</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -538,11 +538,10 @@
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -583,25 +582,20 @@
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>precio_venta_q</t>
+          <t>unidades_paquete</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>unidades_paquete</t>
+          <t>existencia</t>
         </is>
       </c>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>existencia</t>
+          <t>tiempo_entrega_dias</t>
         </is>
       </c>
       <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>tiempo_entrega_dias</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>vencimiento_proximo</t>
         </is>
@@ -696,7 +690,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Supuesto de demostración: la farmacia abre todos los días. Cámbialo si no es así.</t>
+          <t>El sanatorio opera 24 horas todos los días (TuSalud y Facebook).</t>
         </is>
       </c>
     </row>

--- a/datos/plantilla_salvamed.xlsx
+++ b/datos/plantilla_salvamed.xlsx
@@ -731,11 +731,11 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S en quetzales. Escenario base: solo el envío.</t>
+          <t>S en quetzales. Escenario base: unos Q100 de trabajo interno y unos Q50 de flete.</t>
         </is>
       </c>
     </row>
